--- a/AAII_Financials/Yearly/AMPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMPG_YR_FIN.xlsx
@@ -4090,13 +4090,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
